--- a/templates/CAPITANIA CORP FIDC - template.xlsx
+++ b/templates/CAPITANIA CORP FIDC - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$F$42</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="22.28515625" customWidth="1" style="56" min="1" max="1"/>
@@ -741,8 +741,8 @@
     <col width="5.42578125" customWidth="1" style="56" min="7" max="7"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="56" min="8" max="8"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="56" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="56" min="10" max="16"/>
-    <col width="9.140625" customWidth="1" style="56" min="17" max="16384"/>
+    <col width="9.140625" customWidth="1" style="56" min="10" max="17"/>
+    <col width="9.140625" customWidth="1" style="56" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -872,96 +872,96 @@
     <row r="16" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>233.4791211</v>
+        <v>236.07882</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>-0.002668128242064083</v>
+        <v>-0.0006046418704734879</v>
       </c>
       <c r="E16" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F16" s="35" t="n">
-        <v>-0.002775113762013337</v>
+        <v>0.003784363932781476</v>
       </c>
     </row>
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C17" s="37" t="n">
-        <v>234.1037399</v>
+        <v>236.2216495</v>
       </c>
       <c r="D17" s="38" t="n">
-        <v>0.001166080261357338</v>
+        <v>-0.0002299708950405099</v>
       </c>
       <c r="E17" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="38" t="n">
-        <v>0.001280962415003195</v>
+        <v>0.001906502045387226</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C18" s="37" t="n">
-        <v>233.8310741</v>
+        <v>236.2759861</v>
       </c>
       <c r="D18" s="38" t="n">
-        <v>-0.001884747360838435</v>
+        <v>0.0006872887707878306</v>
       </c>
       <c r="E18" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F18" s="38" t="n">
-        <v>-0.002016246470113892</v>
+        <v>0.005962594715911873</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B19" s="36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C19" s="37" t="n">
-        <v>234.2726188</v>
+        <v>236.1137078</v>
       </c>
       <c r="D19" s="38" t="n">
-        <v>0.002055419088214272</v>
+        <v>0.001006794967038926</v>
       </c>
       <c r="E19" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F19" s="38" t="n">
-        <v>0.002323937513367902</v>
+        <v>-8.847376162690601e-05</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C20" s="37" t="n">
-        <v>233.7920781</v>
+        <v>235.8762288</v>
       </c>
       <c r="D20" s="38" t="n">
-        <v>0.001374758948978316</v>
+        <v>0.00749987542838837</v>
       </c>
       <c r="E20" s="38" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>-0.003517165775007047</v>
+        <v>0.001373673909628392</v>
       </c>
     </row>
     <row r="21" ht="15.95" customHeight="1">
@@ -1001,18 +1001,18 @@
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B23" s="39" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C23" s="39" t="inlineStr"/>
       <c r="D23" s="35" t="n">
-        <v>-0.1610523132060925</v>
+        <v>0.00761536261868434</v>
       </c>
       <c r="E23" s="35" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F23" s="35" t="n">
-        <v>-0.008025264155480549</v>
+        <v>0.0157814657880031</v>
       </c>
       <c r="G23" s="40" t="n"/>
     </row>
@@ -1025,13 +1025,13 @@
       </c>
       <c r="C24" s="42" t="inlineStr"/>
       <c r="D24" s="38" t="n">
-        <v>-0.06912911520805076</v>
+        <v>-0.1562207077706904</v>
       </c>
       <c r="E24" s="38" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F24" s="38" t="n">
-        <v>-0.004366530544361868</v>
+        <v>0.02260048556561456</v>
       </c>
       <c r="G24" s="43" t="n"/>
       <c r="H24" s="44" t="n"/>
@@ -1045,13 +1045,13 @@
       </c>
       <c r="C25" s="42" t="inlineStr"/>
       <c r="D25" s="38" t="n">
-        <v>0.01523508640331062</v>
+        <v>-0.05497259404290911</v>
       </c>
       <c r="E25" s="38" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F25" s="38" t="n">
-        <v>0.02705013376004373</v>
+        <v>0.04800146190063681</v>
       </c>
       <c r="G25" s="43" t="n"/>
     </row>
@@ -1064,13 +1064,13 @@
       </c>
       <c r="C26" s="42" t="inlineStr"/>
       <c r="D26" s="38" t="n">
-        <v>-0.005868802737176382</v>
+        <v>-0.001668004364726916</v>
       </c>
       <c r="E26" s="38" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F26" s="38" t="n">
-        <v>0.05228677744302912</v>
+        <v>0.08424100868653972</v>
       </c>
       <c r="G26" s="43" t="n"/>
     </row>
@@ -1083,13 +1083,13 @@
       </c>
       <c r="C27" s="42" t="inlineStr"/>
       <c r="D27" s="38" t="n">
-        <v>0.1545754049760142</v>
+        <v>0.109542881171558</v>
       </c>
       <c r="E27" s="38" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F27" s="38" t="n">
-        <v>0.1198792525684791</v>
+        <v>0.1412381166231067</v>
       </c>
       <c r="G27" s="43" t="n"/>
     </row>
@@ -1097,37 +1097,37 @@
       <c r="A28" s="41" t="n"/>
       <c r="B28" s="42" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C28" s="42" t="inlineStr"/>
       <c r="D28" s="38" t="n">
-        <v>-0.06285439127882786</v>
+        <v>0.148594915928179</v>
       </c>
       <c r="E28" s="38" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>0.01985296752187793</v>
+        <v>0.1602720665516928</v>
       </c>
       <c r="G28" s="43" t="n"/>
     </row>
     <row r="29" ht="15.95" customFormat="1" customHeight="1" s="32">
-      <c r="A29" s="45" t="n"/>
+      <c r="A29" s="41" t="n"/>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C29" s="42" t="inlineStr"/>
       <c r="D29" s="38" t="n">
-        <v>0.1001173502788979</v>
+        <v>-0.05241964063965265</v>
       </c>
       <c r="E29" s="38" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>0.1316812131695793</v>
+        <v>0.04606202995521769</v>
       </c>
       <c r="G29" s="43" t="n"/>
     </row>
@@ -1135,18 +1135,18 @@
       <c r="A30" s="45" t="n"/>
       <c r="B30" s="42" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C30" s="42" t="inlineStr"/>
       <c r="D30" s="38" t="n">
-        <v>0.1422035464813478</v>
+        <v>0.1001173502788979</v>
       </c>
       <c r="E30" s="38" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>-0.02439397265320542</v>
+        <v>0.1316812131695793</v>
       </c>
       <c r="G30" s="43" t="n"/>
     </row>
@@ -1154,164 +1154,183 @@
       <c r="A31" s="45" t="n"/>
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C31" s="42" t="inlineStr"/>
       <c r="D31" s="38" t="n">
-        <v>0.7302111575012595</v>
+        <v>0.1422035464813478</v>
       </c>
       <c r="E31" s="38" t="n">
-        <v>0.7243565410122468</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F31" s="38" t="n">
-        <v>0.3969008009978856</v>
+        <v>-0.02439397265320542</v>
       </c>
       <c r="G31" s="43" t="n"/>
     </row>
-    <row r="32" ht="15.95" customHeight="1">
-      <c r="A32" s="13" t="n"/>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="26.1" customHeight="1">
+    <row r="32" ht="15.95" customFormat="1" customHeight="1" s="32">
+      <c r="A32" s="45" t="n"/>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr"/>
+      <c r="D32" s="38" t="n">
+        <v>0.7494763835383116</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>0.7337368586809545</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>0.4327995643220708</v>
+      </c>
+      <c r="G32" s="43" t="n"/>
+    </row>
+    <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="13" t="n"/>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="26.1" customHeight="1">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="29" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="29" t="n"/>
-      <c r="E33" s="29" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="15.95" customHeight="1">
-      <c r="A34" s="14" t="n"/>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="46" t="n">
-        <v>73702986.3255</v>
-      </c>
-      <c r="F34" s="31" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
     <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="14" t="n"/>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Hoje¹</t>
         </is>
       </c>
       <c r="C35" s="16" t="n"/>
       <c r="D35" s="16" t="n"/>
       <c r="E35" s="46" t="n">
-        <v>137828639.421402</v>
+        <v>74523640.2993</v>
       </c>
       <c r="F35" s="31" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
     <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="14" t="n"/>
-      <c r="B36" s="18" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="46" t="n">
+        <v>135157623.2468365</v>
+      </c>
+      <c r="F36" s="31" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="A37" s="19" t="n"/>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
+      <c r="A38" s="19" t="n"/>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>¹Data de Referência:</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
-      <c r="G37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="21" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="15.95" customHeight="1">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">²Cota Inicial em: </t>
         </is>
       </c>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C39" s="21" t="inlineStr">
         <is>
           <t>2021-04-29</t>
         </is>
       </c>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="4" t="n"/>
-    </row>
-    <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="25" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="23" t="n"/>
       <c r="F39" s="23" t="n"/>
       <c r="G39" s="4" t="n"/>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="55" t="inlineStr">
+    <row r="40" ht="15.95" customHeight="1">
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="23" t="n"/>
+      <c r="F40" s="23" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="57" t="n"/>
       <c r="G41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n"/>
-      <c r="B42" s="26" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
+      <c r="B42" s="57" t="n"/>
       <c r="G42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
+      <c r="B43" s="26" t="n"/>
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="26" t="n"/>
+      <c r="E43" s="26" t="n"/>
+      <c r="F43" s="26" t="n"/>
       <c r="G43" s="4" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="4" t="n"/>
       <c r="B44" s="27" t="n"/>
       <c r="C44" s="28" t="n"/>
       <c r="D44" s="12" t="n"/>
       <c r="E44" s="12" t="n"/>
       <c r="F44" s="12" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="27" t="n"/>
+      <c r="C45" s="28" t="n"/>
+      <c r="D45" s="12" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="89" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="86"/>
 </worksheet>
 </file>